--- a/Docs/asset-index/ASSETS-Index.xlsx
+++ b/Docs/asset-index/ASSETS-Index.xlsx
@@ -17457,7 +17457,7 @@
       </c>
       <c r="M193" s="38" t="inlineStr">
         <is>
-          <t>A lot of very useful props that can be useful for staging in any location</t>
+          <t>A lot of very useful props that can be useful for staging in any location REVIEWED 2026-10-03 and REJECTED for Mr. Moonlight (useful in general, not for this game). Deleted from Playground to save disk; AST-060.zip kept in 01_DOWNLOAD.</t>
         </is>
       </c>
       <c r="N193" s="39" t="inlineStr">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="I196" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J196" s="36" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="M196" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-09-29 — acquired outside the original list.</t>
+          <t>[Claude] Added 2026-09-29 — acquired outside the original list. Moved into Mr. Moonlight 2026-10-03 (props only): Assets/_Project/Art/Environment/MedievalWells (42 FBX with LOD0-2, one RetroLit material, shared atlas pixelated to 1024 / normal 512) and Assets/_Project/Prefabs/World/MedievalWells (42 Prop_ + 23 Set_ prefabs). Skipped: demo scenes, lightmaps, terrain layers, legacy foliage. Still staged in Playground too. Awaiting Carlos review.</t>
         </is>
       </c>
       <c r="N196" s="39" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="K63" s="38" t="inlineStr">
         <is>
-          <t>A lot of very useful props that can be useful for staging in any location</t>
+          <t>A lot of very useful props that can be useful for staging in any location REVIEWED 2026-10-03 and REJECTED for Mr. Moonlight (useful in general, not for this game). Deleted from Playground to save disk; AST-060.zip kept in 01_DOWNLOAD.</t>
         </is>
       </c>
       <c r="L63" s="41" t="n"/>
@@ -43676,7 +43676,7 @@
       </c>
       <c r="I205" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J205" s="38" t="inlineStr">
@@ -43686,7 +43686,7 @@
       </c>
       <c r="K205" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-09-29 — acquired outside the original list.</t>
+          <t>[Claude] Added 2026-09-29 — acquired outside the original list. Moved into Mr. Moonlight 2026-10-03 (props only): Assets/_Project/Art/Environment/MedievalWells (42 FBX with LOD0-2, one RetroLit material, shared atlas pixelated to 1024 / normal 512) and Assets/_Project/Prefabs/World/MedievalWells (42 Prop_ + 23 Set_ prefabs). Skipped: demo scenes, lightmaps, terrain layers, legacy foliage. Still staged in Playground too. Awaiting Carlos review.</t>
         </is>
       </c>
       <c r="L205" s="39" t="n"/>

--- a/Docs/asset-index/ASSETS-Index.xlsx
+++ b/Docs/asset-index/ASSETS-Index.xlsx
@@ -12995,7 +12995,7 @@
       </c>
       <c r="I141" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J141" s="36" t="inlineStr">
@@ -13016,7 +13016,8 @@
       <c r="M141" s="38" t="inlineStr">
         <is>
           <t>Useful for the Church staging
-[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-074); its Packages/manifest.json was skipped. Clean, no input or material fixes needed. Pending move to Mr. Moonlight.</t>
+[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-074); its Packages/manifest.json was skipped. Clean, no input or material fixes needed. Pending move to Mr. Moonlight.
+[Claude] 2026-10-09: all 63 prefabs moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-074 (Graveyard Tombstones)/{Prefabs,Meshes,Materials,Textures}. 9 RetroLit materials, BaseColor pixelated at 512 (normals 256), vendor GUIDs kept, vendor colliders untouched (collider policy not run). Not placed in a scene, not reviewed. Playground copy still staged.</t>
         </is>
       </c>
       <c r="N141" s="41" t="n"/>
@@ -13166,7 +13167,7 @@
       </c>
       <c r="I143" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J143" s="36" t="inlineStr">
@@ -13188,7 +13189,8 @@
         <is>
           <t>Could be useful for staging and props.  Ideally on the dock area
 [Claude] 2026-10-02: owned (downloaded through Package Manager, no file in 01_DOWNLOAD; copied from the Asset Store cache). Staged in Playground as PLAYGROUND/AST-108.
-[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-108). 3 Standard + 2 tree-shader materials converted to URP/Lit; the ivy has no texture in the package (flat green placeholder); 3 Tree components warn that they need the Nature/Soft Occlusion shader. Pending move to Mr. Moonlight.</t>
+[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-108). 3 Standard + 2 tree-shader materials converted to URP/Lit; the ivy has no texture in the package (flat green placeholder); 3 Tree components warn that they need the Nature/Soft Occlusion shader. Pending move to Mr. Moonlight.
+[Claude] 2026-10-09: only The Shed.prefab moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-108 (The Shed)/{Prefabs,Meshes,Materials,Textures}. 5 RetroLit materials; BaseColor pixelated at 2048 (building), 2048 (tools atlas), 1024 (objects) after Carlos found 1024/512 too pixelated; 11 flat-grey decal quads deactivated; colliders added (shell + objects LOD0 mesh colliders, 5 boxes on the tool pieces). Carlos tested it placed in scene 07. Playground copy still staged.</t>
         </is>
       </c>
       <c r="N143" s="41" t="n"/>
@@ -13255,7 +13257,7 @@
       </c>
       <c r="I144" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J144" s="36" t="inlineStr">
@@ -13275,7 +13277,8 @@
       </c>
       <c r="M144" s="38" t="inlineStr">
         <is>
-          <t>[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-162). 108 HDRP/Lit materials converted in place to URP/Lit (local tool AST-162/Editor/HdrpToUrpMaterialConvert.cs, GUIDs kept), 2 unused ones with missing shader graphs set to URP/Lit, missing LOD materials filled. Pending move to Mr. Moonlight.</t>
+          <t>[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-162). 108 HDRP/Lit materials converted in place to URP/Lit (local tool AST-162/Editor/HdrpToUrpMaterialConvert.cs, GUIDs kept), 2 unused ones with missing shader graphs set to URP/Lit, missing LOD materials filled. Pending move to Mr. Moonlight.
+[Claude] 2026-10-10: URP version moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-162 (Swimming Pool)/{Prefabs (148),Meshes (144 FBX),Materials (93),Textures (89)} + Assembled/AbandonedPool_Assembled.prefab (the scene's whole Meshes object as ONE prefab: 3,190 pieces, 13,380 renderers, 3,148 mesh colliders; built in Playground with PrefabUtility). Shader-graph materials rebuilt as RetroLit, BaseColor pixelated at 2048 (large structures) / 1024 (props), never 512 except where the source is 512. Vendor colliders untouched, collider policy not run, not placed in a scene. Playground copy still staged (was deleted by accident and restored from the Recycle Bin 2026-10-10).</t>
         </is>
       </c>
       <c r="N144" s="39" t="inlineStr">
@@ -13611,7 +13614,7 @@
       </c>
       <c r="I148" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J148" s="36" t="inlineStr">
@@ -13631,7 +13634,7 @@
       </c>
       <c r="M148" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-292 (Witch Village)'. HDRP-only pack: materials converted to URP in place (render audit 0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-292 (Witch Village)'. HDRP-only pack: materials converted to URP in place (render audit 0 pink). Not in Mr. Moonlight. [Claude] 2026-10-09: prefabs + particles moved into Mr. Moonlight at Assets/_Project/Art/Buildings &amp; Props/AST-292 (Witch Village)/ (262 prefabs incl. 5 particle prefabs, 251 FBX, 79 RetroLit materials + 5 URP particle/glass materials, 132 textures pixelated to 512 / normals 256, vendor GUIDs kept). Left out: water plane, Shader Graphs, terrain, animations, gallery scenes. Vendor URP package only; Playground copy still staged.</t>
         </is>
       </c>
       <c r="N148" s="39" t="inlineStr">
@@ -34258,7 +34261,7 @@
       </c>
       <c r="I77" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J77" s="38" t="inlineStr">
@@ -34269,7 +34272,8 @@
       <c r="K77" s="38" t="inlineStr">
         <is>
           <t>Useful for the Church staging
-[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-074); its Packages/manifest.json was skipped. Clean, no input or material fixes needed. Pending move to Mr. Moonlight.</t>
+[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-074); its Packages/manifest.json was skipped. Clean, no input or material fixes needed. Pending move to Mr. Moonlight.
+[Claude] 2026-10-09: all 63 prefabs moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-074 (Graveyard Tombstones)/{Prefabs,Meshes,Materials,Textures}. 9 RetroLit materials, BaseColor pixelated at 512 (normals 256), vendor GUIDs kept, vendor colliders untouched (collider policy not run). Not placed in a scene, not reviewed. Playground copy still staged.</t>
         </is>
       </c>
       <c r="L77" s="41" t="n"/>
@@ -36635,7 +36639,7 @@
       </c>
       <c r="I108" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J108" s="38" t="inlineStr">
@@ -36647,7 +36651,8 @@
         <is>
           <t>Could be useful for staging and props.  Ideally on the dock area
 [Claude] 2026-10-02: owned (downloaded through Package Manager, no file in 01_DOWNLOAD; copied from the Asset Store cache). Staged in Playground as PLAYGROUND/AST-108.
-[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-108). 3 Standard + 2 tree-shader materials converted to URP/Lit; the ivy has no texture in the package (flat green placeholder); 3 Tree components warn that they need the Nature/Soft Occlusion shader. Pending move to Mr. Moonlight.</t>
+[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-108). 3 Standard + 2 tree-shader materials converted to URP/Lit; the ivy has no texture in the package (flat green placeholder); 3 Tree components warn that they need the Nature/Soft Occlusion shader. Pending move to Mr. Moonlight.
+[Claude] 2026-10-09: only The Shed.prefab moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-108 (The Shed)/{Prefabs,Meshes,Materials,Textures}. 5 RetroLit materials; BaseColor pixelated at 2048 (building), 2048 (tools atlas), 1024 (objects) after Carlos found 1024/512 too pixelated; 11 flat-grey decal quads deactivated; colliders added (shell + objects LOD0 mesh colliders, 5 boxes on the tool pieces). Carlos tested it placed in scene 07. Playground copy still staged.</t>
         </is>
       </c>
       <c r="L108" s="41" t="n"/>
@@ -40110,7 +40115,7 @@
       </c>
       <c r="I148" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J148" s="38" t="inlineStr">
@@ -40120,7 +40125,8 @@
       </c>
       <c r="K148" s="38" t="inlineStr">
         <is>
-          <t>[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-162). 108 HDRP/Lit materials converted in place to URP/Lit (local tool AST-162/Editor/HdrpToUrpMaterialConvert.cs, GUIDs kept), 2 unused ones with missing shader graphs set to URP/Lit, missing LOD materials filled. Pending move to Mr. Moonlight.</t>
+          <t>[Claude] 2026-10-01: staged in Playground (PLAYGROUND/AST-162). 108 HDRP/Lit materials converted in place to URP/Lit (local tool AST-162/Editor/HdrpToUrpMaterialConvert.cs, GUIDs kept), 2 unused ones with missing shader graphs set to URP/Lit, missing LOD materials filled. Pending move to Mr. Moonlight.
+[Claude] 2026-10-10: URP version moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-162 (Swimming Pool)/{Prefabs (148),Meshes (144 FBX),Materials (93),Textures (89)} + Assembled/AbandonedPool_Assembled.prefab (the scene's whole Meshes object as ONE prefab: 3,190 pieces, 13,380 renderers, 3,148 mesh colliders; built in Playground with PrefabUtility). Shader-graph materials rebuilt as RetroLit, BaseColor pixelated at 2048 (large structures) / 1024 (props), never 512 except where the source is 512. Vendor colliders untouched, collider policy not run, not placed in a scene. Playground copy still staged (was deleted by accident and restored from the Recycle Bin 2026-10-10).</t>
         </is>
       </c>
       <c r="L148" s="41" t="n"/>
@@ -47947,7 +47953,7 @@
       </c>
       <c r="I239" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J239" s="38" t="inlineStr">
@@ -47957,7 +47963,7 @@
       </c>
       <c r="K239" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-292 (Witch Village)'. HDRP-only pack: materials converted to URP in place (render audit 0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-292 (Witch Village)'. HDRP-only pack: materials converted to URP in place (render audit 0 pink). Not in Mr. Moonlight. [Claude] 2026-10-09: prefabs + particles moved into Mr. Moonlight at Assets/_Project/Art/Buildings &amp; Props/AST-292 (Witch Village)/ (262 prefabs incl. 5 particle prefabs, 251 FBX, 79 RetroLit materials + 5 URP particle/glass materials, 132 textures pixelated to 512 / normals 256, vendor GUIDs kept). Left out: water plane, Shader Graphs, terrain, animations, gallery scenes. Vendor URP package only; Playground copy still staged.</t>
         </is>
       </c>
       <c r="L239" s="39" t="n"/>

--- a/Docs/asset-index/ASSETS-Index.xlsx
+++ b/Docs/asset-index/ASSETS-Index.xlsx
@@ -13707,7 +13707,7 @@
       </c>
       <c r="I149" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J149" s="36" t="inlineStr">
@@ -13727,7 +13727,8 @@
       </c>
       <c r="M149" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list; no collection URL recorded. Staged in Playground 2026-10-05 as 'AST-296 (PSX Hospital Church)'. Textures assigned by name (0 pink). The pack's Hospital_horror.zip is an Unreal project, not used. Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list; no collection URL recorded. Staged in Playground 2026-10-05 as 'AST-296 (PSX Hospital Church)'. Textures assigned by name (0 pink). The pack's Hospital_horror.zip is an Unreal project, not used. Not in Mr. Moonlight.
+[Claude] 2026-10-10: the 67 prefabs moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-296 (PSX Hospital Church)/{Prefabs,Meshes (Hospital.fbx),Materials 4,Textures 4}. RetroLit, base only; BaseColor pixelated 1024 (architecture atlas) / 512 (props atlases) - the textures are detailed, not low-res. No colliders; not placed in a scene. Playground copy still staged.</t>
         </is>
       </c>
       <c r="N149" s="41" t="n"/>
@@ -18552,7 +18553,7 @@
       </c>
       <c r="I204" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J204" s="36" t="inlineStr">
@@ -18572,7 +18573,8 @@
       </c>
       <c r="M204" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-293 (Dead Bodies)'. Built-in materials converted to URP in place (0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-293 (Dead Bodies)'. Built-in materials converted to URP in place (0 pink). Not in Mr. Moonlight.
+[Claude] 2026-10-10: the Prefabs folder (156 prefabs) moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-293 (Dead Bodies)/{Prefabs,Meshes (82),Materials (56),Textures (110)}. RetroLit, BaseColor pixelated per material (1024 body-sized, 512 limbs/skulls, 256 hands/feet), DirectX normals flipped, Body_Bag_2 base map fixed. Mega_Blood_Pack not moved; no colliders; Severed_BodyParts_onTable_1 renders blank (vendor defect). Not placed in a scene. Playground copy still staged.</t>
         </is>
       </c>
       <c r="N204" s="39" t="inlineStr">
@@ -18643,7 +18645,7 @@
       </c>
       <c r="I205" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J205" s="36" t="inlineStr">
@@ -18663,7 +18665,8 @@
       </c>
       <c r="M205" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-294 (Barricades)'. Sketchfab rip: 339 skinned meshes, 14 URP materials built and remapped (0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-294 (Barricades)'. Sketchfab rip: 339 skinned meshes, 14 URP materials built and remapped (0 pink). Not in Mr. Moonlight.
+[Claude] 2026-10-10: moved into Mr. Moonlight and SPLIT: the single skinned FBX (339 meshes in a grid) was baked to static meshes and grouped into 124 individual PIECES + 26 pre-built STRUCTURES (Art/Buildings &amp; Props/AST-294 (Barricades)/{Prefabs/Pieces,Prefabs/Structures,Meshes,Materials,Textures}). 14 RetroLit materials, BaseColor pixelated 2048/1024/512 per material. No colliders; not placed in a scene; the original FBX is not in Mr. Moonlight. Playground copy still staged.</t>
         </is>
       </c>
       <c r="N205" s="39" t="inlineStr">
@@ -18734,7 +18737,7 @@
       </c>
       <c r="I206" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J206" s="36" t="inlineStr">
@@ -18754,7 +18757,8 @@
       </c>
       <c r="M206" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-295 (Medieval Furniture)'. HDRP-only pack: materials converted to URP in place (0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-295 (Medieval Furniture)'. HDRP-only pack: materials converted to URP in place (0 pink). Not in Mr. Moonlight.
+[Claude] 2026-10-10: URP re-import (Carlos deleted the mixed HDRP/URP folder) reorganised in Playground as PLAYGROUND/AST-295 (Medieval Furniture), then the Prefabs moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-295 (Medieval Furniture)/{Prefabs 89,Meshes 71,Materials 39,Textures 45}. 36 shader-graph materials -&gt; RetroLit, BaseColor pixelated 1024/512 by prefab size; the 4 PS_ particle prefabs + 3 materials + 3 textures moved as they are; 6 realtime point lights (3 with shadows) and 133 vendor colliders untouched. The 51 HDRP leftover materials in Meshes/Materials were NOT moved (pink, unused). Not placed in a scene.</t>
         </is>
       </c>
       <c r="N206" s="39" t="inlineStr">
@@ -18825,7 +18829,7 @@
       </c>
       <c r="I207" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J207" s="36" t="inlineStr">
@@ -18845,7 +18849,8 @@
       </c>
       <c r="M207" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list; no collection URL recorded. Staged in Playground 2026-10-05 as 'AST-297 (PSX Wooden Fences)'. 71 FBX, no fixes needed (0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list; no collection URL recorded. Staged in Playground 2026-10-05 as 'AST-297 (PSX Wooden Fences)'. 71 FBX, no fixes needed (0 pink). Not in Mr. Moonlight.
+[Claude] 2026-10-10: the 71 prefabs moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-297 (PSX Wooden Fences)/{Prefabs,Meshes 71 baked,Materials 31,Textures 31}. The embedded FBX materials were first extracted to .mat files in Playground. RetroLit, base only; BaseColor pixelated 512 (27) / 256 (4), capped at each texture's effective resolution. No colliders; not placed in a scene. Playground copy still staged.</t>
         </is>
       </c>
       <c r="N207" s="41" t="n"/>
@@ -48040,7 +48045,7 @@
       </c>
       <c r="I240" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J240" s="38" t="inlineStr">
@@ -48050,7 +48055,8 @@
       </c>
       <c r="K240" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-293 (Dead Bodies)'. Built-in materials converted to URP in place (0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-293 (Dead Bodies)'. Built-in materials converted to URP in place (0 pink). Not in Mr. Moonlight.
+[Claude] 2026-10-10: the Prefabs folder (156 prefabs) moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-293 (Dead Bodies)/{Prefabs,Meshes (82),Materials (56),Textures (110)}. RetroLit, BaseColor pixelated per material (1024 body-sized, 512 limbs/skulls, 256 hands/feet), DirectX normals flipped, Body_Bag_2 base map fixed. Mega_Blood_Pack not moved; no colliders; Severed_BodyParts_onTable_1 renders blank (vendor defect). Not placed in a scene. Playground copy still staged.</t>
         </is>
       </c>
       <c r="L240" s="39" t="n"/>
@@ -48127,7 +48133,7 @@
       </c>
       <c r="I241" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J241" s="38" t="inlineStr">
@@ -48137,7 +48143,8 @@
       </c>
       <c r="K241" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-294 (Barricades)'. Sketchfab rip: 339 skinned meshes, 14 URP materials built and remapped (0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-294 (Barricades)'. Sketchfab rip: 339 skinned meshes, 14 URP materials built and remapped (0 pink). Not in Mr. Moonlight.
+[Claude] 2026-10-10: moved into Mr. Moonlight and SPLIT: the single skinned FBX (339 meshes in a grid) was baked to static meshes and grouped into 124 individual PIECES + 26 pre-built STRUCTURES (Art/Buildings &amp; Props/AST-294 (Barricades)/{Prefabs/Pieces,Prefabs/Structures,Meshes,Materials,Textures}). 14 RetroLit materials, BaseColor pixelated 2048/1024/512 per material. No colliders; not placed in a scene; the original FBX is not in Mr. Moonlight. Playground copy still staged.</t>
         </is>
       </c>
       <c r="L241" s="39" t="n"/>
@@ -48214,7 +48221,7 @@
       </c>
       <c r="I242" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J242" s="38" t="inlineStr">
@@ -48224,7 +48231,8 @@
       </c>
       <c r="K242" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-295 (Medieval Furniture)'. HDRP-only pack: materials converted to URP in place (0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list. Staged in Playground 2026-10-05 as 'AST-295 (Medieval Furniture)'. HDRP-only pack: materials converted to URP in place (0 pink). Not in Mr. Moonlight.
+[Claude] 2026-10-10: URP re-import (Carlos deleted the mixed HDRP/URP folder) reorganised in Playground as PLAYGROUND/AST-295 (Medieval Furniture), then the Prefabs moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-295 (Medieval Furniture)/{Prefabs 89,Meshes 71,Materials 39,Textures 45}. 36 shader-graph materials -&gt; RetroLit, BaseColor pixelated 1024/512 by prefab size; the 4 PS_ particle prefabs + 3 materials + 3 textures moved as they are; 6 realtime point lights (3 with shadows) and 133 vendor colliders untouched. The 51 HDRP leftover materials in Meshes/Materials were NOT moved (pink, unused). Not placed in a scene.</t>
         </is>
       </c>
       <c r="L242" s="39" t="n"/>
@@ -48299,7 +48307,7 @@
       </c>
       <c r="I243" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J243" s="38" t="inlineStr">
@@ -48309,7 +48317,8 @@
       </c>
       <c r="K243" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list; no collection URL recorded. Staged in Playground 2026-10-05 as 'AST-296 (PSX Hospital Church)'. Textures assigned by name (0 pink). The pack's Hospital_horror.zip is an Unreal project, not used. Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list; no collection URL recorded. Staged in Playground 2026-10-05 as 'AST-296 (PSX Hospital Church)'. Textures assigned by name (0 pink). The pack's Hospital_horror.zip is an Unreal project, not used. Not in Mr. Moonlight.
+[Claude] 2026-10-10: the 67 prefabs moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-296 (PSX Hospital Church)/{Prefabs,Meshes (Hospital.fbx),Materials 4,Textures 4}. RetroLit, base only; BaseColor pixelated 1024 (architecture atlas) / 512 (props atlases) - the textures are detailed, not low-res. No colliders; not placed in a scene. Playground copy still staged.</t>
         </is>
       </c>
       <c r="L243" s="39" t="n"/>
@@ -48382,7 +48391,7 @@
       </c>
       <c r="I244" s="36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J244" s="38" t="inlineStr">
@@ -48392,7 +48401,8 @@
       </c>
       <c r="K244" s="38" t="inlineStr">
         <is>
-          <t>[Claude] Added 2026-10-05 — acquired outside the original list; no collection URL recorded. Staged in Playground 2026-10-05 as 'AST-297 (PSX Wooden Fences)'. 71 FBX, no fixes needed (0 pink). Not in Mr. Moonlight.</t>
+          <t>[Claude] Added 2026-10-05 — acquired outside the original list; no collection URL recorded. Staged in Playground 2026-10-05 as 'AST-297 (PSX Wooden Fences)'. 71 FBX, no fixes needed (0 pink). Not in Mr. Moonlight.
+[Claude] 2026-10-10: the 71 prefabs moved into Mr. Moonlight: Art/Buildings &amp; Props/AST-297 (PSX Wooden Fences)/{Prefabs,Meshes 71 baked,Materials 31,Textures 31}. The embedded FBX materials were first extracted to .mat files in Playground. RetroLit, base only; BaseColor pixelated 512 (27) / 256 (4), capped at each texture's effective resolution. No colliders; not placed in a scene. Playground copy still staged.</t>
         </is>
       </c>
       <c r="L244" s="39" t="n"/>
